--- a/data/matches/leagues/Finland_Veikkausliiga_2025.xlsx
+++ b/data/matches/leagues/Finland_Veikkausliiga_2025.xlsx
@@ -67912,10 +67912,10 @@
         <v>1</v>
       </c>
       <c r="CX148" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CY148" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CZ148" t="n">
         <v>65</v>
@@ -68079,7 +68079,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -68252,7 +68252,7 @@
         <v>0</v>
       </c>
       <c r="BF149" t="n">
-        <v>-1</v>
+        <v>1335</v>
       </c>
       <c r="BG149" t="n">
         <v>2</v>
@@ -68551,7 +68551,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -68603,16 +68603,16 @@
         <v>3</v>
       </c>
       <c r="S150" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U150" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="V150" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W150" t="n">
         <v>8</v>
@@ -68621,10 +68621,10 @@
         <v>6</v>
       </c>
       <c r="Y150" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z150" t="n">
         <v>47</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>53</v>
       </c>
       <c r="AA150" t="inlineStr"/>
       <c r="AB150" t="inlineStr"/>
@@ -68716,7 +68716,7 @@
         <v>0</v>
       </c>
       <c r="BF150" t="n">
-        <v>-1</v>
+        <v>2910</v>
       </c>
       <c r="BG150" t="n">
         <v>2</v>
@@ -68776,13 +68776,13 @@
         <v>103</v>
       </c>
       <c r="BZ150" t="n">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="CA150" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="CB150" t="n">
-        <v>3.66</v>
+        <v>3.35</v>
       </c>
       <c r="CC150" t="n">
         <v>0</v>
@@ -68839,16 +68839,16 @@
         <v>1</v>
       </c>
       <c r="CU150" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="CV150" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CW150" t="n">
         <v>1</v>
       </c>
       <c r="CX150" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CY150" t="n">
         <v>10</v>
@@ -69172,7 +69172,7 @@
         <v>0</v>
       </c>
       <c r="BF151" t="n">
-        <v>-1</v>
+        <v>6436</v>
       </c>
       <c r="BG151" t="n">
         <v>2</v>
@@ -69459,7 +69459,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -69624,7 +69624,7 @@
         <v>0</v>
       </c>
       <c r="BF152" t="n">
-        <v>-1</v>
+        <v>1864</v>
       </c>
       <c r="BG152" t="n">
         <v>2</v>
@@ -69798,13 +69798,13 @@
         <v>24</v>
       </c>
       <c r="DL152" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DM152" t="n">
         <v>1.3</v>
       </c>
       <c r="DN152" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="DO152" t="n">
         <v>27</v>
@@ -70371,7 +70371,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -70544,7 +70544,7 @@
         <v>0</v>
       </c>
       <c r="BF154" t="n">
-        <v>-1</v>
+        <v>1088</v>
       </c>
       <c r="BG154" t="n">
         <v>2</v>
@@ -70851,7 +70851,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -71024,7 +71024,7 @@
         <v>0</v>
       </c>
       <c r="BF155" t="n">
-        <v>-1</v>
+        <v>2235</v>
       </c>
       <c r="BG155" t="n">
         <v>2</v>
@@ -71968,7 +71968,7 @@
         <v>0</v>
       </c>
       <c r="BF157" t="n">
-        <v>-1</v>
+        <v>3110</v>
       </c>
       <c r="BG157" t="n">
         <v>2</v>
@@ -72719,7 +72719,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -72884,7 +72884,7 @@
         <v>0</v>
       </c>
       <c r="BF159" t="n">
-        <v>-1</v>
+        <v>961</v>
       </c>
       <c r="BG159" t="n">
         <v>2</v>
@@ -73058,13 +73058,13 @@
         <v>21</v>
       </c>
       <c r="DL159" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DM159" t="n">
         <v>1.19</v>
       </c>
       <c r="DN159" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DO159" t="n">
         <v>27</v>
@@ -73183,7 +73183,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -73647,7 +73647,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -73989,10 +73989,10 @@
         <v>1.25</v>
       </c>
       <c r="DM161" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DN161" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="DO161" t="n">
         <v>27</v>
@@ -76459,13 +76459,13 @@
         <v>5</v>
       </c>
       <c r="S167" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T167" t="n">
         <v>9</v>
       </c>
       <c r="U167" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V167" t="n">
         <v>14</v>
@@ -76477,10 +76477,10 @@
         <v>11</v>
       </c>
       <c r="Y167" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="Z167" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
@@ -76580,7 +76580,7 @@
         <v>0</v>
       </c>
       <c r="BF167" t="n">
-        <v>-1</v>
+        <v>1902</v>
       </c>
       <c r="BG167" t="n">
         <v>2</v>
@@ -76640,13 +76640,13 @@
         <v>84</v>
       </c>
       <c r="BZ167" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="CA167" t="n">
         <v>1.57</v>
       </c>
       <c r="CB167" t="n">
-        <v>3.76</v>
+        <v>3.64</v>
       </c>
       <c r="CC167" t="n">
         <v>0</v>
@@ -76703,10 +76703,10 @@
         <v>1</v>
       </c>
       <c r="CU167" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="CV167" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="CW167" t="n">
         <v>1</v>
@@ -77508,7 +77508,7 @@
         <v>0</v>
       </c>
       <c r="BF169" t="n">
-        <v>-1</v>
+        <v>4309</v>
       </c>
       <c r="BG169" t="n">
         <v>2</v>
@@ -77980,7 +77980,7 @@
         <v>0</v>
       </c>
       <c r="BF170" t="n">
-        <v>-1</v>
+        <v>2649</v>
       </c>
       <c r="BG170" t="n">
         <v>2</v>
@@ -78621,10 +78621,10 @@
         <v>1.61</v>
       </c>
       <c r="DM171" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DN171" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="DO171" t="n">
         <v>32</v>
@@ -78805,10 +78805,10 @@
         <v>5</v>
       </c>
       <c r="Y172" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Z172" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AA172" t="inlineStr"/>
       <c r="AB172" t="inlineStr"/>
@@ -78900,7 +78900,7 @@
         <v>0</v>
       </c>
       <c r="BF172" t="n">
-        <v>-1</v>
+        <v>5004</v>
       </c>
       <c r="BG172" t="n">
         <v>2</v>
@@ -81256,7 +81256,7 @@
         <v>0</v>
       </c>
       <c r="BF177" t="n">
-        <v>-1</v>
+        <v>6001</v>
       </c>
       <c r="BG177" t="n">
         <v>2</v>
